--- a/Tabela 1_versão_usada.xlsx
+++ b/Tabela 1_versão_usada.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Página1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,10 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
-  <si>
-    <t>TABELA 1 TCC</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>Zona</t>
   </si>
@@ -227,10 +224,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
@@ -433,163 +426,161 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="C3" s="3">
         <v>209.0</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3">
         <v>210.0</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3">
         <v>210.0</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="5">
         <v>209.0</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
